--- a/Tarifario_sctr.xlsx
+++ b/Tarifario_sctr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCF9167-3C88-4982-A4E0-44DD1F8191C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9645768C-53AF-41C6-9B82-996E1AF6AE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24225" yWindow="4065" windowWidth="21585" windowHeight="11385" xr2:uid="{A800080A-6063-4515-8D0F-5F34B51414F3}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A800080A-6063-4515-8D0F-5F34B51414F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tarifario_sctr" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>Rubro Comercial (Nombre amigable para la web)</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Mapfre Pensión</t>
   </si>
   <si>
-    <t>Servicios Generales, Limpieza y Vigilancia</t>
-  </si>
-  <si>
     <t>Consultoría, Ingeniería y Supervisión (Visita a Obra)</t>
   </si>
   <si>
@@ -68,12 +65,6 @@
     <t>Transporte de Carga y Logística</t>
   </si>
   <si>
-    <t>Metalmecánica, Carpintería y Vidriería</t>
-  </si>
-  <si>
-    <t>Construcción Civil y Obras</t>
-  </si>
-  <si>
     <t>Impuestos</t>
   </si>
   <si>
@@ -126,6 +117,18 @@
   </si>
   <si>
     <t>Generación, transmisión y distribución de energía eléctrica</t>
+  </si>
+  <si>
+    <t>Construcción, Obras y Contratistas</t>
+  </si>
+  <si>
+    <t>Seguridad Privada y Vigilancia</t>
+  </si>
+  <si>
+    <t>Servicios Generales y Limpieza</t>
+  </si>
+  <si>
+    <t>Industria, Manufacturera y Metalmecánica</t>
   </si>
 </sst>
 </file>
@@ -1009,10 +1012,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>0.97</v>
@@ -1041,10 +1044,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>1.46</v>
@@ -1073,10 +1076,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>0.8</v>
@@ -1105,10 +1108,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>0.56999999999999995</v>
@@ -1137,10 +1140,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>1.5</v>
@@ -1169,10 +1172,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>0.82</v>
@@ -1201,10 +1204,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>0.53</v>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>0.44</v>
@@ -1265,10 +1268,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>1.18</v>
@@ -1297,10 +1300,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11">
         <v>1.18</v>
@@ -1329,10 +1332,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12">
         <v>1.03</v>
@@ -1361,10 +1364,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13">
         <v>1.06</v>
@@ -1393,10 +1396,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C14">
         <v>1.01</v>
@@ -1432,10 +1435,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EABD19C-8674-4253-86BD-3BC58EDE1A9A}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1464,7 +1470,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1">
         <v>0.18</v>
@@ -1493,7 +1499,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>60</v>
@@ -1522,7 +1528,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>30</v>
